--- a/Customer_US_Uplaod.xlsx
+++ b/Customer_US_Uplaod.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ciplaltd-my.sharepoint.com/personal/nilesh_bhoir_cipla_com/Documents/Cipla/NB/HANA-S4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC10488C795F68A65BDE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6380D1D-0032-48B5-A71A-BCF3358CBE96}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC10488C795F68A65BDE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58FABA44-A50B-4427-8604-B6CCCBEECEB3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,21 +237,9 @@
     <t>YVMI</t>
   </si>
   <si>
-    <t>VA TN Valley HCS</t>
-  </si>
-  <si>
-    <t>1589 Sparta Street</t>
-  </si>
-  <si>
-    <t>Mcminnville</t>
-  </si>
-  <si>
     <t>US</t>
   </si>
   <si>
-    <t>TN</t>
-  </si>
-  <si>
     <t>EN</t>
   </si>
   <si>
@@ -294,9 +282,6 @@
     <t xml:space="preserve"> DVA</t>
   </si>
   <si>
-    <t>FW3011549</t>
-  </si>
-  <si>
     <t>01.01.2012</t>
   </si>
   <si>
@@ -319,6 +304,21 @@
   </si>
   <si>
     <t>FN1162940</t>
+  </si>
+  <si>
+    <t>James E Van Zandt VAMC</t>
+  </si>
+  <si>
+    <t>800 Howard Avenue</t>
+  </si>
+  <si>
+    <t>Altoona</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>BA4482814</t>
   </si>
 </sst>
 </file>
@@ -731,6 +731,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BU3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="34.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -972,37 +975,37 @@
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="7"/>
       <c r="S2" s="8"/>
       <c r="T2" s="9">
-        <v>37110</v>
+        <v>29732</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
@@ -1016,20 +1019,20 @@
         <v>2270001</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AI2" s="6"/>
       <c r="AJ2" s="6"/>
       <c r="AK2" s="6"/>
       <c r="AL2" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AM2" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AN2" s="6"/>
       <c r="AO2" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AP2" s="6">
         <v>100</v>
@@ -1038,27 +1041,27 @@
         <v>5401</v>
       </c>
       <c r="AR2" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AS2" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AT2" s="6"/>
       <c r="AU2" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AV2" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AW2" s="6">
         <v>1</v>
       </c>
       <c r="AX2" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AY2" s="6"/>
       <c r="AZ2" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BA2" s="6">
         <v>5400</v>
@@ -1067,32 +1070,32 @@
         <v>9</v>
       </c>
       <c r="BC2" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="BD2" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="BE2" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="BF2" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BG2" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BH2" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BI2" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BJ2" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BK2" s="10"/>
       <c r="BL2" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="BM2" s="6"/>
       <c r="BN2" s="6"/>
@@ -1101,23 +1104,22 @@
         <v>5400</v>
       </c>
       <c r="BQ2" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="BR2" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BS2" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="BT2" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BU2" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:73" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
       <c r="B3" s="4">
         <v>5400</v>
       </c>
@@ -1133,39 +1135,39 @@
       <c r="F3" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="7"/>
       <c r="S3" s="8"/>
       <c r="T3" s="9">
-        <v>29732</v>
+        <v>16601</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
@@ -1179,20 +1181,20 @@
         <v>2270001</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AI3" s="6"/>
       <c r="AJ3" s="6"/>
       <c r="AK3" s="6"/>
       <c r="AL3" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AM3" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AN3" s="6"/>
       <c r="AO3" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AP3" s="6">
         <v>100</v>
@@ -1201,27 +1203,27 @@
         <v>5401</v>
       </c>
       <c r="AR3" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AS3" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AV3" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AW3" s="6">
         <v>1</v>
       </c>
       <c r="AX3" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AY3" s="6"/>
       <c r="AZ3" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BA3" s="6">
         <v>5400</v>
@@ -1230,32 +1232,32 @@
         <v>9</v>
       </c>
       <c r="BC3" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="BD3" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="BE3" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="BF3" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BG3" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BH3" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BI3" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BJ3" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="BK3" s="10"/>
       <c r="BL3" s="10" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="BM3" s="6"/>
       <c r="BN3" s="6"/>
@@ -1267,16 +1269,16 @@
         <v>97</v>
       </c>
       <c r="BR3" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BS3" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="BT3" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BU3" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
